--- a/合成表.xlsx
+++ b/合成表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s04024026\Desktop\無機３\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s04024026\Desktop\無機３\my_streamlit_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFAEA67-0AFC-4798-A4DE-4AC9382C7CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE5B70F-D6AB-4406-8322-F2B77CD8681A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" xr2:uid="{4FC1890B-E7E1-4EBE-81B3-90D98BD5E7F4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$163</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="282">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -1815,6 +1815,106 @@
     <t>銅</t>
     <rPh sb="0" eb="1">
       <t>ドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガリウム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲルマニウム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヘキサフルオロケイ酸</t>
+    <rPh sb="9" eb="10">
+      <t>サン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>二酸化ケイ素</t>
+    <rPh sb="0" eb="3">
+      <t>ニサンカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フッ化水素</t>
+    <rPh sb="2" eb="5">
+      <t>カスイソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>臭化銀</t>
+    <rPh sb="0" eb="3">
+      <t>シュウカギン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>銀</t>
+    <rPh sb="0" eb="1">
+      <t>ギン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>臭素</t>
+    <rPh sb="0" eb="2">
+      <t>シュウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニホニウム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>謎の物質</t>
+    <rPh sb="0" eb="1">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブッシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニクロム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニッケル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クロム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フッ化銀</t>
+    <rPh sb="2" eb="4">
+      <t>カギン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フッ素</t>
+    <rPh sb="2" eb="3">
+      <t>ソ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2210,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D97AA0-A8A6-4EA9-AB75-22DA04741D9D}">
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="20.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -2547,308 +2647,299 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
-        <v>259</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>259</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>181</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>169</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>175</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>187</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>246</v>
+        <v>43</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
-        <v>46</v>
+        <v>243</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>159</v>
+        <v>244</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>223</v>
+        <v>189</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
-        <v>236</v>
+        <v>53</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>154</v>
@@ -2856,250 +2947,241 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
-        <v>56</v>
+        <v>236</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>192</v>
+        <v>165</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>176</v>
+        <v>191</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>148</v>
+        <v>58</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
-        <v>63</v>
+        <v>272</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>205</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
-        <v>251</v>
+        <v>70</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E82" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>165</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>242</v>
-      </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>165</v>
@@ -3107,363 +3189,375 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>170</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>150</v>
+        <v>210</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>217</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>193</v>
+        <v>166</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>235</v>
+        <v>161</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
-        <v>84</v>
+        <v>194</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>165</v>
+        <v>235</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E99" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>219</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>220</v>
+        <v>157</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>150</v>
+        <v>201</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>171</v>
+        <v>222</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
-        <v>100</v>
+        <v>276</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>165</v>
+        <v>279</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
-        <v>104</v>
+        <v>237</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>227</v>
+        <v>154</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>165</v>
@@ -3471,324 +3565,400 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1" t="s">
-        <v>110</v>
+        <v>275</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>150</v>
+        <v>227</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>217</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="1" t="s">
-        <v>117</v>
+        <v>280</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="1" t="s">
-        <v>123</v>
+        <v>268</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>165</v>
+        <v>270</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>240</v>
+        <v>121</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="1" t="s">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>240</v>
+        <v>165</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="1" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E146" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>231</v>
+        <v>129</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>233</v>
+        <v>166</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C164" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>263</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F155" xr:uid="{40D97AA0-A8A6-4EA9-AB75-22DA04741D9D}"/>
+  <autoFilter ref="A1:F163" xr:uid="{40D97AA0-A8A6-4EA9-AB75-22DA04741D9D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/合成表.xlsx
+++ b/合成表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s04024026\Desktop\無機３\my_streamlit_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE5B70F-D6AB-4406-8322-F2B77CD8681A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB2E486-5FE3-461D-A1DD-85F81E2AB66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12300" xr2:uid="{4FC1890B-E7E1-4EBE-81B3-90D98BD5E7F4}"/>
+    <workbookView xWindow="2660" yWindow="800" windowWidth="3910" windowHeight="11280" xr2:uid="{4FC1890B-E7E1-4EBE-81B3-90D98BD5E7F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="282">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -2472,9 +2472,6 @@
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>255</v>
       </c>
@@ -3843,14 +3840,14 @@
       <c r="A154" s="1" t="s">
         <v>133</v>
       </c>
+      <c r="B154" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="C154" s="1" t="s">
         <v>161</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>165</v>
+        <v>240</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.55000000000000004">
